--- a/input.xlsx
+++ b/input.xlsx
@@ -1,128 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76D9C883-E70E-4AE5-864B-A2C751A420EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dataset" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
-  <si>
-    <t>prompt</t>
-  </si>
-  <si>
-    <t>expected_value</t>
-  </si>
-  <si>
-    <t>What currency was used for the booking with hotel code SHGMH and check-in date August 20 2015?</t>
-  </si>
-  <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t>What is the room type code for the booking at hotel SHGMH with confirmation number 67738126?</t>
-  </si>
-  <si>
-    <t>OQNS</t>
-  </si>
-  <si>
-    <t>What was the total room rate amount for the booking at hotel MQEAP with confirmation number 68259404?</t>
-  </si>
-  <si>
-    <t>75.34</t>
-  </si>
-  <si>
-    <t>What currency was used for the booking at hotel MQEAP with confirmation number 68259404?</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>What is the first name of the guest for the booking at hotel MSPRG with confirmation number 46159042?</t>
-  </si>
-  <si>
-    <t>Bruce</t>
-  </si>
-  <si>
-    <t>What is the last name of the guest for the booking at hotel MSPRG with confirmation number 46159042?</t>
-  </si>
-  <si>
-    <t>Britton</t>
-  </si>
-  <si>
-    <t>What is the hotel code for the booking with guest Graciela Marshall and check-in date April 21 2026?</t>
-  </si>
-  <si>
-    <t>FLLRS</t>
-  </si>
-  <si>
-    <t>What is the room number for the stay at hotel FLLRS for guest Graciela Marshall?</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>What is the currency used for the booking with confirmation number 25770978 at hotel NYCMA?</t>
-  </si>
-  <si>
-    <t>What is the first name of the guest for the booking at hotel NYCMA with confirmation number 25770978?</t>
-  </si>
-  <si>
-    <t>FRITZLER</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -130,27 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -438,100 +420,536 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="100" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>prompt</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>expected_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>What is the total food revenue () in USD from completed stays at hotel 'ATHGR' in November 2025?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>{"total_food_rev_usd": 65444.430019}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>List all unique corporate account numbers () that stayed at hotel 'MLBOC' with a stay starting after August 1st, 2020.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[{"CORP_ACCT_NBR":"1"},{"CORP_ACCT_NBR":"100005167"},{"CORP_ACCT_NBR":"100007951"},{"CORP_ACCT_NBR":"100008021"},{"CORP_ACCT_NBR":"100008994"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Find the average check-in rate () for bookings cancelled with a penalty indicator set to 'Y' in the brand 'CP'.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>{"avg_cancelled_rate": 2252.026300717}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>What is the highest daily room rate in USD () recorded in the day-level details for check-outs on '2020-08-09'?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>{"max_daily_rate": 17577}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Calculate the total beverage charge () for stays that checked in between '2020-08-01' and '2020-08-15' at hotel 'CHIEL'.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>{"total_bev_charge": 0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>How many distinct loyalty memberships () received points from stays at brand 'HI' during 2020?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{"count_mbrshp": 3192204}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>List the top 5 room types () by total room revenue () for completed bookings.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[{"RM_TYP_CD":"PM","total_rev":26388087395.58},{"RM_TYP_CD":"OQNN","total_rev":25450751748.22},{"RM_TYP_CD":"KNGN","total_rev":12620324399.62},{"RM_TYP_CD":"TQNN","total_rev":11780767683.55},{"RM_TYP_CD":"TTWN","total_rev":9762277074.1}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>What is the total number of nights () booked where the sell channel code was 'WEB' in the last quarter of 2025?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>{"sum_accom_nt_qty": 23450630}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Find the maximum penalty amount () charged for cancelled stays in 2025.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>{"max_bkg_pnlty_amt": null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>How many bookings have a difference between check-in date () and confirmation date () of more than 30 days?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{"count": 689935923}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Show the total miscellaneous pet charges () by hotel code () for stays in 2025.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[{"HTL_CD":"XNVUK","pet_charge":"0"},{"HTL_CD":"MAATP","pet_charge":"0"},{"HTL_CD":"PHXUP","pet_charge":"0"},{"HTL_CD":"BJASC","pet_charge":"0"},{"HTL_CD":"BLIHI","pet_charge":"0"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>What is the total net qualifying revenue in USD () for members whose preferred alliance () is 'HPC'?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"total_net_qual_rev_usd": 138730508991.7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>List all stays where more than 3 guests () were registered at hotel 'ATHGR'.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[{"BKG_CONF_NBR":"-100616764","BKG_CK_IN_DT":null,"HTL_CD":"ATHGR","STY_GST_QTY":"4","BKG_TOT_RM_RATE_AMT":null}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Find the total non-revenue tax charge () for hotel 'MLBOC' in 2025.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{"total_non_rev_tax": 914717.009938}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>What is the average number of nights () per booking for each booking channel ()?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[{"SELL_CHNL_CD":"UNK","avg_nights":13.5341324682254}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Count the number of reservations that did not participate in the full folio program ( = 'N').</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>{"total_rows": 23112111}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Find the total room rates booked vs actually stayed at 'ATHGR' in 2025.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>{"booked_revenue":23992592.66,"actual_revenue":10025467.7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Calculate the total commission due () for bookings checked out on '2025-11-17'.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>{"total_comm": null}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Show the total meeting and banquet revenue () grouped by original rate category code ().</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>[{"ORIG_RATE_CATGY_CD":null,"total_rev":"2051252656463.890105"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>List all checkout dates with an average stay length of more than 5 nights at hotel 'ATHGR'.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[{"BKG_CK_OUT_DT":"2023-12-31","avg_nights":"334.04845814977961"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>How are bookings doing recently?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Find our best-performing hotel code.</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>What is the average rate?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Show our current occupancy levels.</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>What is the total revenue for the CP chain?</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Show the leisure bookings trend.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Predict our future room revenue for the next 12 months using external market indicators.</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>List the ratings and text reviews of hotel 'ATHGR' submitted by TripAdvisor users.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>What was the average temperature and weather impact on bookings at our Chicago properties?</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>How does our competitor's Average Daily Rate (ADR) compare to our properties in Europe?</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>What is the loyalty member's lifetime tier level (e.g., Gold, Platinum) for member ID 102455?</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Show the parking lot usage fees and parking occupancy rate for hotel 'MLBOC'.</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>List the email addresses and phone numbers of guests who stayed in August 2020.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>What is the total discount amount applied to the booking segment using coupon codes?</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Filter the stays by the guest's age group and demographic category.</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>List the employee ID of the receptionist who checked in guest confirmation '855723'.</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>What are the total carbon emissions and sustainability scores of stays at 'ATHGR'?</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>What is the total number of bookings that stayed in August 2020?</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>{"total_bookings": 4856425}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Find the total number of stays that occurred at hotel 'CHIEL'.</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>{"count_pms_conf": 343852}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Calculate the total actual room revenue generated in USD on August 8, 2020, across all hotels.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>{"daily_rev": 45364833.85}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>How many total room-nights were spent in August 2020?</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>{"total_room_nights": 5424852}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>What is the average room rate per night for stays in brand 'CP' during 2025?</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Show the total number of distinct nights spent grouped by sequence number ().</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>[{"DY_SEQ_NBR":"1","total_nights":"1665809584"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Calculate total room rate revenue booked vs actually realized in USD for hotel 'ATHGR' in 2025.</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>[{"booked_revenue":"23992592.66","actual_revenue":"10025467.7"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Show the most valuable corporate accounts based on total spend in 2025.</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>[{"CORP_ACCT_NBR":"100860933","total_spend":"165854494.21"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>List our underperforming rate categories by average check-in rate.</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Find the highest quality stays based on score metrics.</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>[{"PMS_CONF_NBR":"018924592","STY_FRST_NM":"Jen","STY_LST_NM":"Chi","total_score":"4"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Show the most successful booking channel by volume of reservations.</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>[{"SELL_CHNL_CD":"INN","booking_volume":"3121523327"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Identify the hotels that are most successful at enrolling new members.</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>[{"HTL_CD":"ZYLEA","total_enrollments":"684334"}]</t>
+        </is>
       </c>
     </row>
   </sheetData>
